--- a/build/custom-roles-run/CustomRoles_Support_QuickReference.xlsx
+++ b/build/custom-roles-run/CustomRoles_Support_QuickReference.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Every role has a work-order 'view mode'. FULL view shows the complete work order, including the line Approve action and financial actions. TECH view is a simpler, technician-focused screen that hides the Approve action and some other controls — good for people who do the work but shouldn't approve or see everything.</t>
+          <t>Every role has a work-order 'view mode'. FULL view shows the complete work order, including the per-line Approve/Decline buttons and the bulk-approve control. TECH view is a simpler, technician-focused screen that HIDES the Approve/Decline actions (and the bulk-approve control) — good for people who do the work but shouldn't approve. Note: seeing dollar amounts is a separate setting ('See Financial Data'), not the view mode.</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Ordering parts on a work order.</t>
+          <t>Ordering parts on a work order. It also controls the work order's PARTS tab: with Order Parts on, the Parts tab appears; with it off, the Parts tab is hidden.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Inside a work order (parts/ordering actions).</t>
+          <t>Inside a work order (the Parts tab and the ordering actions).</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Picking in-stock parts for a work order.</t>
+          <t>Picking in-stock parts for a work order. (Does not by itself show the Parts tab — the Parts tab is controlled by Order Parts.)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1053,12 +1053,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Add Parts (work-order sub-permission)</t>
+          <t>Review Work Orders (work-order sub-permission)</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Adding a part to a work-order line.</t>
+          <t>The Review sign-off step on a work order. Until Review is done, Create Invoice stays disabled.</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1073,24 +1073,24 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Inside a work order &gt; line &gt; Request/Add part.</t>
+          <t>Inside a work order (Review action).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (work-order sub-permission)</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>The Review sign-off step on a work order. Until Review is done, Create Invoice stays disabled.</t>
+          <t>Whether the user sees dollar amounts on work orders, parts and invoices, and whether the Finance tab appears.</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Single on/off sub-permission under Work Orders.</t>
+          <t>Cross-cutting toggle (on/off).</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1100,19 +1100,19 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Inside a work order (Review action).</t>
+          <t>Everywhere money shows: work orders, parts cost/price columns, invoices, the Finance tab.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>Manage Accounts Payable &amp; Receivable (AP/AR)</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Whether the user sees dollar amounts on work orders, parts and invoices, and whether the Finance tab appears.</t>
+          <t>The 7 sensitive customer fields (Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min &amp; Max, Taxes, 'PO is required') and the customer AP/AR tabs. Today it also controls access to the AP/AR aging reports.</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1127,19 +1127,19 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Everywhere money shows: work orders, parts cost/price columns, invoices, the Finance tab.</t>
+          <t>Customer record (sensitive fields + AP/AR tabs); AP/AR aging reports.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Manage Accounts Payable &amp; Receivable (AP/AR)</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>The 7 sensitive customer fields (Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min &amp; Max, Taxes, 'PO is required') and the customer AP/AR tabs. Today it also controls access to the AP/AR aging reports.</t>
+          <t>The work-order history. This is one combined history that shows BOTH work-order-level changes (e.g. the work order being created) AND line-level changes (e.g. a line being created/changed — the line 'story'). Work orders only — there is no history for Part Sales or Purchase Orders.</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1154,34 +1154,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Customer record (sensitive fields + AP/AR tabs); AP/AR aging reports.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>View History Logs</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>The work-order history: the work-order-level Audit Log/History and the line-level story/history. Work orders only — there is no history for Part Sales or Purchase Orders.</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Cross-cutting toggle (on/off).</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Inside a work order (History / Audit Log; line story).</t>
+          <t>Inside a work order (the History tab / Audit Log; line story).</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1724,156 +1697,168 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Full view is the complete work-order screen, including the line Approve action and financial actions. Tech view is a simpler, technician-focused screen that hides the Approve action and some other controls — ideal for people who do the work but shouldn't approve or see everything.</t>
+          <t>Full view is the complete work-order screen, including the per-line Approve/Decline buttons and the bulk-approve control. Tech view is a simpler, technician-focused screen that hides those approve actions — ideal for people who do the work but shouldn't approve. Seeing dollar amounts is a separate setting ('See Financial Data'), not the view mode.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>How do I stop a role from seeing prices / dollar amounts?</t>
+          <t>Which permission shows or hides the Parts tab on a work order?</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Turn off 'See Financial Data' for that role. With it off, dollar amounts are hidden on work orders, parts and invoices, and the Finance tab won't appear at all.</t>
+          <t>The 'Order Parts' permission (under Work Orders). With Order Parts on, the work order's Parts tab appears; with it off, the Parts tab is hidden. (Pick Parts on its own does not show the tab.)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>How do I control who sees the AP/AR aging reports?</t>
+          <t>How do I stop a role from seeing prices / dollar amounts?</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Right now, access to the AP/AR aging reports is controlled by the 'Manage Accounts Payable &amp; Receivable' permission (in addition to Reports access). Turn that off for roles that shouldn't see aging reports.</t>
+          <t>Turn off 'See Financial Data' for that role. With it off, dollar amounts are hidden on work orders, parts and invoices, and the Finance tab won't appear at all.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>How do I hide the sensitive customer fields (credit terms, limits, etc.)?</t>
+          <t>How do I control who sees the AP/AR aging reports?</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Those 7 fields (Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min &amp; Max, Taxes, 'PO is required') are controlled by 'Manage Accounts Payable &amp; Receivable'. Turn it off to hide them; the basic customer fields stay visible.</t>
+          <t>Right now, access to the AP/AR aging reports is controlled by the 'Manage Accounts Payable &amp; Receivable' permission (in addition to Reports access). Turn that off for roles that shouldn't see aging reports.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Why can a user edit or delete a note they didn't create?</t>
+          <t>How do I hide the sensitive customer fields (credit terms, limits, etc.)?</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>That's how work-order notes work. Anyone with Work Orders: View (create/edit) can create and edit ANY note on a work order, and anyone with Work Orders: Delete can delete ANY note — notes aren't limited to their author.</t>
+          <t>Those 7 fields (Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min &amp; Max, Taxes, 'PO is required') are controlled by 'Manage Accounts Payable &amp; Receivable'. Turn it off to hide them; the basic customer fields stay visible.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Why can't this role delete a role I created?</t>
+          <t>Why can a user edit or delete a note they didn't create?</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>A role can only be deleted when no users are assigned to it. Reassign the users off the role first, then the Delete option becomes available.</t>
+          <t>That's how work-order notes work. Anyone with Work Orders: View (create/edit) can create and edit ANY note on a work order, and anyone with Work Orders: Delete can delete ANY note — notes aren't limited to their author.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Why did a user get logged out right after I changed their role?</t>
+          <t>Why can't this role delete a role I created?</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>That's expected. Changing someone's role ends their current session immediately; the new permissions apply the next time they log in.</t>
+          <t>A role can only be deleted when no users are assigned to it. Reassign the users off the role first, then the Delete option becomes available.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Why won't my new custom role save?</t>
+          <t>Why did a user get logged out right after I changed their role?</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>A role needs a name AND at least one permission turned on. Also, the name must be unique — a duplicate name is rejected, and a duplicate set of permissions prompts a 'similar role already exists' confirmation.</t>
+          <t>That's expected. Changing someone's role ends their current session immediately; the new permissions apply the next time they log in.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Can the Administrator role be edited or removed?</t>
+          <t>Why won't my new custom role save?</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Administrator can be opened but always keeps full access (its switches are locked on), and no system role — including Administrator — can be deleted. Only Office and Time Clock are fully locked/view-only.</t>
+          <t>A role needs a name AND at least one permission turned on. Also, the name must be unique — a duplicate name is rejected, and a duplicate set of permissions prompts a 'similar role already exists' confirmation.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Where does 'View Permissions' live for a role?</t>
+          <t>Can the Administrator role be edited or removed?</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>For Office and Time Clock there's an eye icon in the Actions column. For every other role (system or custom), View Permissions is inside the three-dot menu.</t>
+          <t>Administrator can be opened but always keeps full access (its switches are locked on), and no system role — including Administrator — can be deleted. Only Office and Time Clock are fully locked/view-only.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Does Part Sales or a Purchase Order have a history log?</t>
+          <t>Where does 'View Permissions' live for a role?</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No. The history/audit log ('View History Logs') covers work orders only — both the work-order-level history and the line-level story. There is no history log for Part Sales or Purchase Orders.</t>
+          <t>For Office and Time Clock there's an eye icon in the Actions column. For every other role (system or custom), View Permissions is inside the three-dot menu.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>What does 'Review Work Orders' do?</t>
+          <t>Does Part Sales or a Purchase Order have a history log?</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>It controls the Review sign-off step on a work order. Until the Review step is completed, the Create Invoice button stays disabled.</t>
+          <t>No. The history/audit log ('View History Logs') covers work orders only — both the work-order-level history and the line-level story. There is no history log for Part Sales or Purchase Orders.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>What does 'Review Work Orders' do?</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>It controls the Review sign-off step on a work order. Until the Review step is completed, the Create Invoice button stays disabled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>Turning on Delete also turned on Create &amp; Edit and View — is that a bug?</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>No, that's intended. For any resource, Delete requires Create &amp; Edit and View, so switching Delete on turns those on too. Likewise, turning View off clears everything under that resource.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Coming soon (not live yet — do not promise these today): the AP/AR aging reports are planned to move to the Reports permission only; the role editor is planned to auto-link Order Parts with See Financial Data; and QuickBooks is planned to move under Finance settings. Until then, describe today's behaviour above.</t>
         </is>
@@ -1881,7 +1866,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1951,36 +1936,36 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>"They can't order parts on a work order."</t>
+          <t>"There's no Parts tab on the work order."</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Turn on 'Order Parts' (under Work Orders) together with 'See Financial Data'.</t>
+          <t>Turn on 'Order Parts' (under Work Orders) — it controls the Parts tab. Pick Parts alone does not show the tab.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>"They can't pick in-stock parts."</t>
+          <t>"They can't order parts on a work order."</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Turn on 'Pick Parts' (under Work Orders).</t>
+          <t>Turn on 'Order Parts' (under Work Orders) together with 'See Financial Data'.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>"They can't add a part to a line."</t>
+          <t>"They can't pick in-stock parts."</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Turn on 'Add Parts' (under Work Orders).</t>
+          <t>Turn on 'Pick Parts' (under Work Orders).</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2250,12 +2235,24 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Not fully verified</t>
+          <t>Verified in live VIU (2026-07-07)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>WO Parts tab gating by Order Parts is unconfirmed; line-level (vs WO-level) history was not separately exercised; the core OK/Not-OK control was not driven end-to-end.</t>
+          <t>Confirmed on staging: (a) Order Parts controls the WO Parts tab (on shows / off hides; gated by Order Parts, not Pick Parts); (b) View History Logs is one feed carrying both WO-level and line-level events, work-orders-only (part-sales/PO history endpoints 404); (c) Full-vs-Tech view: Tech view hides per-line Approve/Decline and the bulk-approve icon and relabels hours 'Total Tech Hours' — money visibility is governed by See Financial Data, not view mode; (d) authoritative permission catalog captured (41 Admin atoms) in permission-catalog-source.json. There is NO separate 'Add Parts' permission atom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Still not fully verified</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Core OK/Not-OK: the core UI surface is confirmed live (Parts grid 'Core' column; inventory core fields), but the OK/Not-OK action itself was not driven end-to-end (needs a manually-seeded received core part). Governed per spec by Work Order Lines: Create &amp; Edit.</t>
         </is>
       </c>
     </row>
